--- a/data/trans_orig/P35-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P35-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007 (tasa de respuesta: 95,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40371</t>
+          <t>41809</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65276</t>
+          <t>67134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>46439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74342</t>
+          <t>74063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92626</t>
+          <t>94337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131053</t>
+          <t>132967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195423</t>
+          <t>193565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220328</t>
+          <t>218890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182135</t>
+          <t>182414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210809</t>
+          <t>210038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>386122</t>
+          <t>384208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>424549</t>
+          <t>422838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88936</t>
+          <t>90777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127116</t>
+          <t>126675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136427</t>
+          <t>136651</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176178</t>
+          <t>175874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>238417</t>
+          <t>238486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>294498</t>
+          <t>294119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338095</t>
+          <t>338536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376275</t>
+          <t>374434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300591</t>
+          <t>300895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>340342</t>
+          <t>340118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647482</t>
+          <t>647861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703563</t>
+          <t>703494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55560</t>
+          <t>55034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47726</t>
+          <t>48258</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74456</t>
+          <t>75711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85991</t>
+          <t>83419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121396</t>
+          <t>121077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>252151</t>
+          <t>252677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276165</t>
+          <t>276565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251178</t>
+          <t>249923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277908</t>
+          <t>277376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>511949</t>
+          <t>512268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547354</t>
+          <t>549926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47991</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75757</t>
+          <t>74286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67778</t>
+          <t>68146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99648</t>
+          <t>98390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124205</t>
+          <t>123285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166691</t>
+          <t>165050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>266381</t>
+          <t>267852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>294147</t>
+          <t>293521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246962</t>
+          <t>248220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278832</t>
+          <t>278464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>522057</t>
+          <t>523698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>564543</t>
+          <t>565463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>27620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37072</t>
+          <t>37671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32519</t>
+          <t>33470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59282</t>
+          <t>58778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164854</t>
+          <t>164421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180472</t>
+          <t>180983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160749</t>
+          <t>160150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>180448</t>
+          <t>179552</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>330581</t>
+          <t>331085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357344</t>
+          <t>356393</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41914</t>
+          <t>41356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67906</t>
+          <t>66825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48140</t>
+          <t>48158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74968</t>
+          <t>74539</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131916</t>
+          <t>133973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184909</t>
+          <t>185990</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210901</t>
+          <t>211459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181248</t>
+          <t>181677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208076</t>
+          <t>208058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377115</t>
+          <t>375058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>413533</t>
+          <t>412419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63300</t>
+          <t>62933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95117</t>
+          <t>94224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68634</t>
+          <t>67678</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103021</t>
+          <t>104408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139411</t>
+          <t>140299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>185770</t>
+          <t>186685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>498220</t>
+          <t>499113</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>530037</t>
+          <t>530404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>503673</t>
+          <t>502286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>538060</t>
+          <t>539016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1014261</t>
+          <t>1013346</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1060620</t>
+          <t>1059732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116699</t>
+          <t>116228</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157738</t>
+          <t>158388</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>137604</t>
+          <t>137285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183332</t>
+          <t>183661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>265272</t>
+          <t>261631</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>324811</t>
+          <t>324510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>555532</t>
+          <t>554882</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>596571</t>
+          <t>597042</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>558480</t>
+          <t>558151</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>604208</t>
+          <t>604527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1130271</t>
+          <t>1130572</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1189810</t>
+          <t>1193451</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>504055</t>
+          <t>510422</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>589433</t>
+          <t>590682</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>643049</t>
+          <t>645355</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>737446</t>
+          <t>734471</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1182969</t>
+          <t>1178787</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1304283</t>
+          <t>1297968</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2537790</t>
+          <t>2536541</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2623168</t>
+          <t>2616801</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2470587</t>
+          <t>2473562</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2564984</t>
+          <t>2562678</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5030973</t>
+          <t>5037288</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5152287</t>
+          <t>5156469</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012 (tasa de respuesta: 97,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53666</t>
+          <t>54281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85832</t>
+          <t>83776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96809</t>
+          <t>96074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131738</t>
+          <t>131263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157597</t>
+          <t>156184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201903</t>
+          <t>203166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196417</t>
+          <t>198473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228583</t>
+          <t>227968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151035</t>
+          <t>151510</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185964</t>
+          <t>186699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>363119</t>
+          <t>361856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>407425</t>
+          <t>408838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164394</t>
+          <t>164752</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>210424</t>
+          <t>211973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205180</t>
+          <t>206041</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253261</t>
+          <t>254393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>383424</t>
+          <t>381999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>450040</t>
+          <t>448903</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>287722</t>
+          <t>286173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333752</t>
+          <t>333394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>261347</t>
+          <t>260215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>309428</t>
+          <t>308567</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>562713</t>
+          <t>563850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>629329</t>
+          <t>630754</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60863</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91232</t>
+          <t>91259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>82933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116954</t>
+          <t>117217</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148954</t>
+          <t>150001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194817</t>
+          <t>195941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227478</t>
+          <t>227451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257847</t>
+          <t>258109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219079</t>
+          <t>218816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254690</t>
+          <t>253100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459925</t>
+          <t>458801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>505788</t>
+          <t>504741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43758</t>
+          <t>44849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75178</t>
+          <t>74956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99989</t>
+          <t>99730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135739</t>
+          <t>136878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152220</t>
+          <t>153785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200515</t>
+          <t>202315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282850</t>
+          <t>283072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314270</t>
+          <t>313179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227750</t>
+          <t>226611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263500</t>
+          <t>263759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>521002</t>
+          <t>519202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569297</t>
+          <t>567732</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>35020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60977</t>
+          <t>60213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63451</t>
+          <t>65323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92778</t>
+          <t>93160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108183</t>
+          <t>105691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143409</t>
+          <t>145658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148545</t>
+          <t>149309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173875</t>
+          <t>174502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125925</t>
+          <t>125543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155252</t>
+          <t>153380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284816</t>
+          <t>282567</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320042</t>
+          <t>322534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,32%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63990</t>
+          <t>64284</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95231</t>
+          <t>95594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88909</t>
+          <t>89222</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122617</t>
+          <t>121925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162457</t>
+          <t>160696</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209479</t>
+          <t>207108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175910</t>
+          <t>175547</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207151</t>
+          <t>206857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153727</t>
+          <t>154419</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187435</t>
+          <t>187122</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>338005</t>
+          <t>340376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385027</t>
+          <t>386788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149304</t>
+          <t>149483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196079</t>
+          <t>195095</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>201938</t>
+          <t>203601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252969</t>
+          <t>253132</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>366644</t>
+          <t>362482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434140</t>
+          <t>434938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>453506</t>
+          <t>454490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>500281</t>
+          <t>500102</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>428705</t>
+          <t>428542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>479736</t>
+          <t>478073</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>897119</t>
+          <t>896321</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>964615</t>
+          <t>968777</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,77%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157325</t>
+          <t>156095</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206021</t>
+          <t>207730</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190789</t>
+          <t>193007</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>243695</t>
+          <t>245289</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>363304</t>
+          <t>361009</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>438288</t>
+          <t>435679</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>534133</t>
+          <t>532424</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>582829</t>
+          <t>584059</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>534796</t>
+          <t>533202</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>587702</t>
+          <t>585484</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1080357</t>
+          <t>1082966</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1155341</t>
+          <t>1157636</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>808315</t>
+          <t>808044</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>918082</t>
+          <t>923851</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1128156</t>
+          <t>1128096</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1243553</t>
+          <t>1245567</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1976645</t>
+          <t>1982308</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2138551</t>
+          <t>2128182</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2409452</t>
+          <t>2403683</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2519219</t>
+          <t>2519490</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2208561</t>
+          <t>2206547</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2323958</t>
+          <t>2324018</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4641097</t>
+          <t>4651466</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4803003</t>
+          <t>4797340</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016 (tasa de respuesta: 98,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83686</t>
+          <t>84268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118640</t>
+          <t>117139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109838</t>
+          <t>111271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142728</t>
+          <t>145105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204145</t>
+          <t>203994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251189</t>
+          <t>251577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171155</t>
+          <t>172656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206109</t>
+          <t>205527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145975</t>
+          <t>143598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178865</t>
+          <t>177432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327309</t>
+          <t>326921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374353</t>
+          <t>374504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121091</t>
+          <t>121249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160210</t>
+          <t>160755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165950</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>211106</t>
+          <t>211247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>298190</t>
+          <t>298512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358334</t>
+          <t>358590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342365</t>
+          <t>341820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381484</t>
+          <t>381326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307860</t>
+          <t>307719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353016</t>
+          <t>353015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>663207</t>
+          <t>662951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723351</t>
+          <t>723029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67992</t>
+          <t>68354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98087</t>
+          <t>98608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94231</t>
+          <t>94276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129101</t>
+          <t>128327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171681</t>
+          <t>170378</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218410</t>
+          <t>215147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213684</t>
+          <t>213163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243779</t>
+          <t>243417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205214</t>
+          <t>205988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240084</t>
+          <t>240039</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>427675</t>
+          <t>430938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>474404</t>
+          <t>475707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94272</t>
+          <t>94896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130520</t>
+          <t>129050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124401</t>
+          <t>124711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164989</t>
+          <t>162448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229553</t>
+          <t>230192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282873</t>
+          <t>284227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236535</t>
+          <t>238005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272783</t>
+          <t>272159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217457</t>
+          <t>219998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>258045</t>
+          <t>257735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>466628</t>
+          <t>465274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519948</t>
+          <t>519309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71490</t>
+          <t>70609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99063</t>
+          <t>98463</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96359</t>
+          <t>95754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124197</t>
+          <t>124230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>175812</t>
+          <t>172695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215246</t>
+          <t>213681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110647</t>
+          <t>111247</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138220</t>
+          <t>139101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94390</t>
+          <t>94357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122228</t>
+          <t>122833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213051</t>
+          <t>214616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252485</t>
+          <t>255602</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,68%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72651</t>
+          <t>72493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70918</t>
+          <t>71110</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100311</t>
+          <t>100599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124875</t>
+          <t>124697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166252</t>
+          <t>164937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186810</t>
+          <t>186968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214150</t>
+          <t>214289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169812</t>
+          <t>169524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>199205</t>
+          <t>199013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>363332</t>
+          <t>364647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>404709</t>
+          <t>404887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,45%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170415</t>
+          <t>169838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220440</t>
+          <t>218577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>214010</t>
+          <t>215431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>264910</t>
+          <t>265678</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>400137</t>
+          <t>396506</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>469789</t>
+          <t>465584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>418574</t>
+          <t>420437</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>468599</t>
+          <t>469176</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>410838</t>
+          <t>410070</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>461738</t>
+          <t>460317</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>844973</t>
+          <t>849178</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>914625</t>
+          <t>918256</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137567</t>
+          <t>137966</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>182695</t>
+          <t>181556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187092</t>
+          <t>188334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>240426</t>
+          <t>239761</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>339647</t>
+          <t>338937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>408644</t>
+          <t>408873</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>577444</t>
+          <t>578583</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>622572</t>
+          <t>622173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>566636</t>
+          <t>567301</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>619970</t>
+          <t>618728</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1158558</t>
+          <t>1158329</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1227555</t>
+          <t>1228265</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>874749</t>
+          <t>878132</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>984567</t>
+          <t>981053</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1157730</t>
+          <t>1148481</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1281273</t>
+          <t>1268184</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2070915</t>
+          <t>2071546</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2231270</t>
+          <t>2225499</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2354953</t>
+          <t>2358467</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2464771</t>
+          <t>2461388</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2214676</t>
+          <t>2227765</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2338219</t>
+          <t>2347468</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4604199</t>
+          <t>4609970</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4764554</t>
+          <t>4763923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53249</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25499</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41856</t>
+          <t>42294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57362</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87137</t>
+          <t>87509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258194</t>
+          <t>259320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281613</t>
+          <t>282801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247779</t>
+          <t>247341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264136</t>
+          <t>263460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>513940</t>
+          <t>513568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543715</t>
+          <t>542164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172766</t>
+          <t>173365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233022</t>
+          <t>231232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191507</t>
+          <t>190129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231088</t>
+          <t>229957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>376476</t>
+          <t>378536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>448375</t>
+          <t>446845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>285368</t>
+          <t>287158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345624</t>
+          <t>345025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283150</t>
+          <t>284281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322731</t>
+          <t>324109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>584253</t>
+          <t>585783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656152</t>
+          <t>654092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73909</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101771</t>
+          <t>102989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87306</t>
+          <t>86235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116084</t>
+          <t>114545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167952</t>
+          <t>169678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210259</t>
+          <t>209803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214279</t>
+          <t>213061</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>242141</t>
+          <t>243014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232639</t>
+          <t>234178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>261417</t>
+          <t>262488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>454515</t>
+          <t>454971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>496822</t>
+          <t>495096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53314</t>
+          <t>52243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83600</t>
+          <t>84113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54446</t>
+          <t>58138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118859</t>
+          <t>122466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120209</t>
+          <t>114659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192146</t>
+          <t>191433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228957</t>
+          <t>228444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259243</t>
+          <t>260314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356859</t>
+          <t>353252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>421272</t>
+          <t>417580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596128</t>
+          <t>596841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>668065</t>
+          <t>673615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44170</t>
+          <t>42810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64531</t>
+          <t>63687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53722</t>
+          <t>53347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72021</t>
+          <t>71173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101291</t>
+          <t>103559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130402</t>
+          <t>131425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114211</t>
+          <t>115055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134572</t>
+          <t>135932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135446</t>
+          <t>136294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153745</t>
+          <t>154120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255807</t>
+          <t>254784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284918</t>
+          <t>282650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69046</t>
+          <t>69497</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95510</t>
+          <t>94720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67281</t>
+          <t>67528</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87680</t>
+          <t>88775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141607</t>
+          <t>142330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175736</t>
+          <t>175677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174126</t>
+          <t>174916</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200590</t>
+          <t>200139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169376</t>
+          <t>168281</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189775</t>
+          <t>189528</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>350956</t>
+          <t>351015</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385085</t>
+          <t>384362</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126063</t>
+          <t>127071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>169568</t>
+          <t>171380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105063</t>
+          <t>111420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291678</t>
+          <t>292034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227444</t>
+          <t>241565</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431087</t>
+          <t>432663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>454711</t>
+          <t>452899</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>498216</t>
+          <t>497208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>556755</t>
+          <t>556399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>743370</t>
+          <t>737013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1041625</t>
+          <t>1040049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1245268</t>
+          <t>1231147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>177241</t>
+          <t>186647</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>575996</t>
+          <t>571656</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>445258</t>
+          <t>449839</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>491191</t>
+          <t>492062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>556795</t>
+          <t>542223</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1052390</t>
+          <t>1054883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,18%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>352724</t>
+          <t>357064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>751479</t>
+          <t>742073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>223658</t>
+          <t>222787</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>269591</t>
+          <t>265010</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>591180</t>
+          <t>588687</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1086775</t>
+          <t>1101347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>862249</t>
+          <t>843324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1204823</t>
+          <t>1198696</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1043356</t>
+          <t>1005768</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1361965</t>
+          <t>1371118</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2032995</t>
+          <t>2048831</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2509442</t>
+          <t>2530350</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2254994</t>
+          <t>2261121</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2597568</t>
+          <t>2616493</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2294154</t>
+          <t>2285001</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2612763</t>
+          <t>2650351</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4606494</t>
+          <t>4585586</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5082941</t>
+          <t>5067105</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P35-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41809</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67134</t>
+          <t>66239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>46616</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74063</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94337</t>
+          <t>94294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132967</t>
+          <t>130619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193565</t>
+          <t>194460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218890</t>
+          <t>219905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182414</t>
+          <t>183237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210038</t>
+          <t>209861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>384208</t>
+          <t>386556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>422838</t>
+          <t>422881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90777</t>
+          <t>89146</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126675</t>
+          <t>127038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136651</t>
+          <t>136632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175874</t>
+          <t>178382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>238486</t>
+          <t>234911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>294119</t>
+          <t>293378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338536</t>
+          <t>338173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374434</t>
+          <t>376065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300895</t>
+          <t>298387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>340118</t>
+          <t>340137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647861</t>
+          <t>648602</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703494</t>
+          <t>707069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>30288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48258</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75711</t>
+          <t>75815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83419</t>
+          <t>84919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121077</t>
+          <t>121958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>252677</t>
+          <t>253322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276565</t>
+          <t>277423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249923</t>
+          <t>249819</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277376</t>
+          <t>277184</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>512268</t>
+          <t>511387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>549926</t>
+          <t>548426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>48470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>75484</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>70542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98390</t>
+          <t>101471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123285</t>
+          <t>125429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165050</t>
+          <t>166319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267852</t>
+          <t>266654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293521</t>
+          <t>293668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>248220</t>
+          <t>245139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278464</t>
+          <t>276068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>523698</t>
+          <t>522429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>565463</t>
+          <t>563319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33470</t>
+          <t>33417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58778</t>
+          <t>58742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164421</t>
+          <t>165495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180983</t>
+          <t>181431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160150</t>
+          <t>159903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179552</t>
+          <t>179896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331085</t>
+          <t>331121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356393</t>
+          <t>356446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41356</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66825</t>
+          <t>67224</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48158</t>
+          <t>48233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74539</t>
+          <t>74859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96612</t>
+          <t>92467</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133973</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185990</t>
+          <t>185591</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211459</t>
+          <t>211189</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181677</t>
+          <t>181357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208058</t>
+          <t>207983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>375058</t>
+          <t>377947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412419</t>
+          <t>416564</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62933</t>
+          <t>61802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94224</t>
+          <t>92403</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67678</t>
+          <t>68891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104408</t>
+          <t>102109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140299</t>
+          <t>142120</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186685</t>
+          <t>187324</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>499113</t>
+          <t>500934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>530404</t>
+          <t>531535</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>502286</t>
+          <t>504585</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>539016</t>
+          <t>537803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1013346</t>
+          <t>1012707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1059732</t>
+          <t>1057911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116228</t>
+          <t>117422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>158388</t>
+          <t>159235</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>137285</t>
+          <t>136155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183661</t>
+          <t>180786</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>261631</t>
+          <t>263921</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>324510</t>
+          <t>323809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>554882</t>
+          <t>554035</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>597042</t>
+          <t>595848</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>558151</t>
+          <t>561026</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>604527</t>
+          <t>605657</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1130572</t>
+          <t>1131273</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1193451</t>
+          <t>1191161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>510422</t>
+          <t>508961</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>590682</t>
+          <t>587680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>645355</t>
+          <t>647402</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>734471</t>
+          <t>744599</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1178787</t>
+          <t>1179306</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1297968</t>
+          <t>1298809</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2536541</t>
+          <t>2539543</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2616801</t>
+          <t>2618262</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2473562</t>
+          <t>2463434</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2562678</t>
+          <t>2560631</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5037288</t>
+          <t>5036447</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5156469</t>
+          <t>5155950</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54281</t>
+          <t>54548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83776</t>
+          <t>84335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96074</t>
+          <t>96203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131263</t>
+          <t>132083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156184</t>
+          <t>159875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203166</t>
+          <t>206860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198473</t>
+          <t>197914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>227968</t>
+          <t>227701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151510</t>
+          <t>150690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186699</t>
+          <t>186570</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>361856</t>
+          <t>358162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>408838</t>
+          <t>405147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164752</t>
+          <t>166003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211973</t>
+          <t>210529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206041</t>
+          <t>203736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254393</t>
+          <t>250564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>381999</t>
+          <t>383665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>448903</t>
+          <t>449138</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286173</t>
+          <t>287617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333394</t>
+          <t>332143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>260215</t>
+          <t>264044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308567</t>
+          <t>310872</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>563850</t>
+          <t>563615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>630754</t>
+          <t>629088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60601</t>
+          <t>61726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91259</t>
+          <t>91450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82933</t>
+          <t>81826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117217</t>
+          <t>116411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150001</t>
+          <t>150838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195941</t>
+          <t>195750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227451</t>
+          <t>227260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>258109</t>
+          <t>256984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218816</t>
+          <t>219622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>253100</t>
+          <t>254207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>458801</t>
+          <t>458992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>504741</t>
+          <t>503904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44849</t>
+          <t>44381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>73813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99730</t>
+          <t>100656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136878</t>
+          <t>136450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153785</t>
+          <t>152447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202315</t>
+          <t>198483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283072</t>
+          <t>284215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313179</t>
+          <t>313647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>226611</t>
+          <t>227039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263759</t>
+          <t>262833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>519202</t>
+          <t>523034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>567732</t>
+          <t>569070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35020</t>
+          <t>35118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60213</t>
+          <t>59628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65323</t>
+          <t>64437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93160</t>
+          <t>93813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105691</t>
+          <t>106522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145658</t>
+          <t>143930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>149309</t>
+          <t>149894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174502</t>
+          <t>174404</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125543</t>
+          <t>124890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153380</t>
+          <t>154266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282567</t>
+          <t>284295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322534</t>
+          <t>321703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64284</t>
+          <t>65044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95594</t>
+          <t>95001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89222</t>
+          <t>91133</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>121925</t>
+          <t>124037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>160696</t>
+          <t>163269</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207108</t>
+          <t>207652</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175547</t>
+          <t>176140</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206857</t>
+          <t>206097</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154419</t>
+          <t>152307</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187122</t>
+          <t>185211</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>340376</t>
+          <t>339832</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>386788</t>
+          <t>384215</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149483</t>
+          <t>148296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195095</t>
+          <t>197679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>203601</t>
+          <t>201631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>253132</t>
+          <t>254521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>362482</t>
+          <t>366897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434938</t>
+          <t>431474</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>454490</t>
+          <t>451906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>500102</t>
+          <t>501289</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>428542</t>
+          <t>427153</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>478073</t>
+          <t>480043</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>896321</t>
+          <t>899785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>968777</t>
+          <t>964362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>156095</t>
+          <t>155958</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>207730</t>
+          <t>206413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>193007</t>
+          <t>193669</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>245289</t>
+          <t>244576</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>361009</t>
+          <t>362508</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>435679</t>
+          <t>430151</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>532424</t>
+          <t>533741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>584059</t>
+          <t>584196</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>533202</t>
+          <t>533915</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>585484</t>
+          <t>584822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1082966</t>
+          <t>1088494</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1157636</t>
+          <t>1156137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>808044</t>
+          <t>808272</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>923851</t>
+          <t>912678</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1128096</t>
+          <t>1132348</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1245567</t>
+          <t>1251401</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1982308</t>
+          <t>1977435</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2128182</t>
+          <t>2130614</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2403683</t>
+          <t>2414856</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2519490</t>
+          <t>2519262</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2206547</t>
+          <t>2200713</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2324018</t>
+          <t>2319766</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4651466</t>
+          <t>4649034</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4797340</t>
+          <t>4802213</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84268</t>
+          <t>84379</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117139</t>
+          <t>117045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111271</t>
+          <t>111229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145105</t>
+          <t>144853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203994</t>
+          <t>206163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251577</t>
+          <t>253558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172656</t>
+          <t>172750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205527</t>
+          <t>205416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143598</t>
+          <t>143850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>177432</t>
+          <t>177474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>326921</t>
+          <t>324940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374504</t>
+          <t>372335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121249</t>
+          <t>121026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160755</t>
+          <t>161331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165951</t>
+          <t>163669</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>211247</t>
+          <t>212131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>298512</t>
+          <t>300037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358590</t>
+          <t>359161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341820</t>
+          <t>341244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381326</t>
+          <t>381549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307719</t>
+          <t>306835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353015</t>
+          <t>355297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>662951</t>
+          <t>662380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723029</t>
+          <t>721504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68354</t>
+          <t>69105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>98091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94276</t>
+          <t>92990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128327</t>
+          <t>128333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170378</t>
+          <t>169926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215147</t>
+          <t>217544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213163</t>
+          <t>213680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243417</t>
+          <t>242666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205988</t>
+          <t>205982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240039</t>
+          <t>241325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>430938</t>
+          <t>428541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>475707</t>
+          <t>476159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94896</t>
+          <t>95046</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>129519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124711</t>
+          <t>123391</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162448</t>
+          <t>163540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>230192</t>
+          <t>229652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284227</t>
+          <t>285513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238005</t>
+          <t>237536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272159</t>
+          <t>272009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219998</t>
+          <t>218906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>257735</t>
+          <t>259055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>465274</t>
+          <t>463988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519309</t>
+          <t>519849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70609</t>
+          <t>71617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98463</t>
+          <t>98371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95754</t>
+          <t>94527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124230</t>
+          <t>124109</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172695</t>
+          <t>174629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213681</t>
+          <t>214903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111247</t>
+          <t>111339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139101</t>
+          <t>138093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94357</t>
+          <t>94478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122833</t>
+          <t>124060</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214616</t>
+          <t>213394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255602</t>
+          <t>253668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45172</t>
+          <t>44691</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72493</t>
+          <t>72921</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71110</t>
+          <t>68590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100599</t>
+          <t>100229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124697</t>
+          <t>122401</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164937</t>
+          <t>163440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186968</t>
+          <t>186540</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214289</t>
+          <t>214770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169524</t>
+          <t>169894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>199013</t>
+          <t>201533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>364647</t>
+          <t>366144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>404887</t>
+          <t>407183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,89%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>169838</t>
+          <t>168425</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218577</t>
+          <t>220046</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>215431</t>
+          <t>212911</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>265678</t>
+          <t>263990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396506</t>
+          <t>399363</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>465584</t>
+          <t>467065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>420437</t>
+          <t>418968</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>469176</t>
+          <t>470589</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>410070</t>
+          <t>411758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>460317</t>
+          <t>462837</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>849178</t>
+          <t>847697</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>918256</t>
+          <t>915399</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137966</t>
+          <t>137994</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181556</t>
+          <t>182621</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188334</t>
+          <t>185024</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>239761</t>
+          <t>237613</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>338937</t>
+          <t>336810</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>408873</t>
+          <t>406702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>578583</t>
+          <t>577518</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>622173</t>
+          <t>622145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>567301</t>
+          <t>569449</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>618728</t>
+          <t>622038</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1158329</t>
+          <t>1160500</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1228265</t>
+          <t>1230392</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>878132</t>
+          <t>879891</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>981053</t>
+          <t>986707</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1148481</t>
+          <t>1163670</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1268184</t>
+          <t>1273608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2071546</t>
+          <t>2076240</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2225499</t>
+          <t>2232777</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2358467</t>
+          <t>2352813</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2461388</t>
+          <t>2459629</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2227765</t>
+          <t>2222341</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2347468</t>
+          <t>2332279</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4609970</t>
+          <t>4602692</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4763923</t>
+          <t>4759229</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>40439</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28642</t>
+          <t>30299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52123</t>
+          <t>52588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42294</t>
+          <t>42243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>71618</t>
+          <t>74861</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58913</t>
+          <t>62673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87509</t>
+          <t>90240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>272959</t>
+          <t>278406</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259320</t>
+          <t>266257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282801</t>
+          <t>288546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>256501</t>
+          <t>281639</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247341</t>
+          <t>273818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263460</t>
+          <t>289532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>529459</t>
+          <t>560045</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>513568</t>
+          <t>544666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>542164</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>201308</t>
+          <t>209414</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173365</t>
+          <t>180075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231232</t>
+          <t>237199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>210540</t>
+          <t>224960</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190129</t>
+          <t>204010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229957</t>
+          <t>245652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>411848</t>
+          <t>434374</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>378536</t>
+          <t>399284</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446845</t>
+          <t>467897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>317082</t>
+          <t>321233</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>287158</t>
+          <t>293448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345025</t>
+          <t>350572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>303698</t>
+          <t>320812</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>284281</t>
+          <t>300120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>341762</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>620780</t>
+          <t>642045</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>585783</t>
+          <t>608522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>654092</t>
+          <t>677135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514238</t>
+          <t>545772</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514238</t>
+          <t>545772</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514238</t>
+          <t>545772</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032628</t>
+          <t>1076419</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032628</t>
+          <t>1076419</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032628</t>
+          <t>1076419</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87571</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73036</t>
+          <t>74337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102989</t>
+          <t>104398</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>101230</t>
+          <t>104283</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86235</t>
+          <t>91034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114545</t>
+          <t>118813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>188801</t>
+          <t>193606</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169678</t>
+          <t>173229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209803</t>
+          <t>213477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>228479</t>
+          <t>226670</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213061</t>
+          <t>211595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243014</t>
+          <t>241656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>247493</t>
+          <t>251689</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234178</t>
+          <t>237159</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>262488</t>
+          <t>264938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>475973</t>
+          <t>478359</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>454971</t>
+          <t>458488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>495096</t>
+          <t>498736</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67015</t>
+          <t>83005</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52243</t>
+          <t>65705</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84113</t>
+          <t>105572</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92557</t>
+          <t>104001</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58138</t>
+          <t>87698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122466</t>
+          <t>122934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>159571</t>
+          <t>187007</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114659</t>
+          <t>164239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191433</t>
+          <t>215131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>245542</t>
+          <t>290140</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228444</t>
+          <t>267573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>260314</t>
+          <t>307440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>383161</t>
+          <t>317960</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353252</t>
+          <t>299027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>417580</t>
+          <t>334263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>628703</t>
+          <t>608100</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596841</t>
+          <t>579976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>673615</t>
+          <t>630868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>53225</t>
+          <t>60348</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42810</t>
+          <t>51051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63687</t>
+          <t>72817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62732</t>
+          <t>68234</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53347</t>
+          <t>58361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71173</t>
+          <t>79285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>115957</t>
+          <t>128581</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103559</t>
+          <t>112531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131425</t>
+          <t>144170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>125517</t>
+          <t>145317</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115055</t>
+          <t>132848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135932</t>
+          <t>154614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>144735</t>
+          <t>157744</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136294</t>
+          <t>146693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154120</t>
+          <t>167617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>270252</t>
+          <t>303061</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254784</t>
+          <t>287472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282650</t>
+          <t>319111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207467</t>
+          <t>225978</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207467</t>
+          <t>225978</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207467</t>
+          <t>225978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386209</t>
+          <t>431642</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386209</t>
+          <t>431642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386209</t>
+          <t>431642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81566</t>
+          <t>79949</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69497</t>
+          <t>67679</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94720</t>
+          <t>92045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77248</t>
+          <t>79971</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>69571</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88775</t>
+          <t>91856</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>158814</t>
+          <t>159920</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142330</t>
+          <t>143258</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175677</t>
+          <t>176021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>188070</t>
+          <t>190758</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174916</t>
+          <t>178662</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200139</t>
+          <t>203028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>179808</t>
+          <t>183779</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168281</t>
+          <t>171894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189528</t>
+          <t>194179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>367878</t>
+          <t>374537</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>351015</t>
+          <t>358436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384362</t>
+          <t>391199</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,2%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>147385</t>
+          <t>174142</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127071</t>
+          <t>151819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171380</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>215135</t>
+          <t>258758</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111420</t>
+          <t>235311</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>292034</t>
+          <t>283724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>362520</t>
+          <t>432900</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241565</t>
+          <t>400575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>432663</t>
+          <t>468925</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>476894</t>
+          <t>545545</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>452899</t>
+          <t>518812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>497208</t>
+          <t>567868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>633298</t>
+          <t>512435</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>556399</t>
+          <t>487469</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>737013</t>
+          <t>535882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1110192</t>
+          <t>1057980</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1040049</t>
+          <t>1021955</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1231147</t>
+          <t>1090305</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848433</t>
+          <t>771193</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848433</t>
+          <t>771193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848433</t>
+          <t>771193</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472712</t>
+          <t>1490880</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472712</t>
+          <t>1490880</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472712</t>
+          <t>1490880</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>415108</t>
+          <t>477950</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>186647</t>
+          <t>447283</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>571656</t>
+          <t>506859</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>471058</t>
+          <t>538482</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>449839</t>
+          <t>507851</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>492062</t>
+          <t>563014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>886167</t>
+          <t>1016431</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>542223</t>
+          <t>974090</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1054883</t>
+          <t>1054189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>513612</t>
+          <t>320122</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>357064</t>
+          <t>291213</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>742073</t>
+          <t>350789</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>243791</t>
+          <t>291514</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>222787</t>
+          <t>266982</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>265010</t>
+          <t>322145</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>757403</t>
+          <t>611637</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588687</t>
+          <t>573879</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1101347</t>
+          <t>653978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714849</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714849</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714849</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643570</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643570</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643570</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1091663</t>
+          <t>1214570</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>843324</t>
+          <t>1154652</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1198696</t>
+          <t>1279714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1263634</t>
+          <t>1413111</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1005768</t>
+          <t>1363945</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1371118</t>
+          <t>1468276</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2355296</t>
+          <t>2627681</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2048831</t>
+          <t>2555255</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2530350</t>
+          <t>2717022</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2368154</t>
+          <t>2318192</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2261121</t>
+          <t>2253048</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2616493</t>
+          <t>2378110</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2392485</t>
+          <t>2317572</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2285001</t>
+          <t>2262407</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2650351</t>
+          <t>2366738</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4760640</t>
+          <t>4635764</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4585586</t>
+          <t>4546423</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5067105</t>
+          <t>4708190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
